--- a/data/trans_orig/KIDMED_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65471</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56682</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73687</t>
+          <t>74315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84265</t>
+          <t>85934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96107</t>
+          <t>96767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>211</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>149737</t>
+          <t>151821</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132936</t>
+          <t>136183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163519</t>
+          <t>166487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>59416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>80225</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66822</t>
+          <t>63379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97207</t>
+          <t>94106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55665</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47556</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62663</t>
+          <t>63728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>58988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49358</t>
+          <t>49877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66222</t>
+          <t>66409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>164</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>113608</t>
+          <t>115447</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102502</t>
+          <t>102523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124446</t>
+          <t>126168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30413</t>
+          <t>29073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>37482</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>67136</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56286</t>
+          <t>54602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78416</t>
+          <t>76981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1632,37 +1632,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>34535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48731</t>
+          <t>48916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,47 +1692,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76588</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -1745,37 +1745,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,47 +1805,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43247</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2088,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>109595</t>
+          <t>110399</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129956</t>
+          <t>132143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>133223</t>
+          <t>134865</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117705</t>
+          <t>119892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146057</t>
+          <t>148817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>338</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>242818</t>
+          <t>245265</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196974</t>
+          <t>192805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270070</t>
+          <t>271239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>97631</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76523</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141825</t>
+          <t>135355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74130</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61427</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89932</t>
+          <t>86936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>172565</t>
+          <t>170119</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144844</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218194</t>
+          <t>222566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2544,107 +2544,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>71866</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61913</t>
+          <t>61956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80120</t>
+          <t>80976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>92483</t>
+          <t>93006</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70222</t>
+          <t>70040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105860</t>
+          <t>106250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>164349</t>
+          <t>165404</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142090</t>
+          <t>140394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181285</t>
+          <t>182168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50996</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>62922</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88046</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>117</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>104596</t>
+          <t>103541</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87704</t>
+          <t>87590</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>127752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41187</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>51009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81709</t>
+          <t>82104</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3456,107 +3456,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>575</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>384610</t>
+          <t>387562</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>331623</t>
+          <t>329203</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>413212</t>
+          <t>416766</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>602</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>454310</t>
+          <t>459189</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>425367</t>
+          <t>428358</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>479909</t>
+          <t>486251</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>838921</t>
+          <t>846751</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>782687</t>
+          <t>786273</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>879295</t>
+          <t>884898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -3569,107 +3569,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>243967</t>
+          <t>241015</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>214568</t>
+          <t>212028</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>299529</t>
+          <t>300449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>292</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>255217</t>
+          <t>250338</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>231707</t>
+          <t>224358</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>288122</t>
+          <t>284780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>595</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>499183</t>
+          <t>491353</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>457883</t>
+          <t>449918</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>558307</t>
+          <t>554288</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KIDMED_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
+          <t>Menores según tipo de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80325</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71148</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89732</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55979</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74315</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85934</t>
+          <t>66868</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72586</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96767</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>151821</t>
+          <t>147193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136183</t>
+          <t>134901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166487</t>
+          <t>159375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38159</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29232</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47069</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31948</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23986</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41353</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46192</t>
+          <t>29404</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59416</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>67563</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63379</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94106</t>
+          <t>79804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3874</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8700</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58988</t>
+          <t>58357</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66409</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>115738</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102523</t>
+          <t>104150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>126535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27238</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19915</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35869</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>39,91%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36217</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>29073</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44567</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>65297</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>53195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3623</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3764</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11484</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39884</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>44941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>59,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34535</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28746</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39782</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>68,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>75977</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>67281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>83939</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9292</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20500</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14780</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9585</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20891</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6129</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126178</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>139388</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>110399</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>74595</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>132143</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134865</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119892</t>
+          <t>89884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148817</t>
+          <t>111886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>245265</t>
+          <t>227838</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192805</t>
+          <t>209656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271239</t>
+          <t>245049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66373</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54547</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81296</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>97631</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>75157</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>135355</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,3%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72487</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86936</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>170119</t>
+          <t>133648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144214</t>
+          <t>117019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222566</t>
+          <t>152398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10515</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>67077</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>98338</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>46,07%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>72398</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>61956</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>80976</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>53,64%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106250</t>
+          <t>82798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>165404</t>
+          <t>161101</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140394</t>
+          <t>142154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182168</t>
+          <t>175924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56450</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>44197</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>40620</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>32201</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>51250</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86279</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>94173</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87590</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127752</t>
+          <t>114248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8827</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6429</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42709</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>35383</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>49434</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>47884</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>41584</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>53830</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>49063</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>54801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>91822</t>
+          <t>91773</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82104</t>
+          <t>81492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101534</t>
+          <t>100748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -3113,72 +3113,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>14309</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>27264</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>19820</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>13871</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>26167</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29044</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>40194</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>49736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8347</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>432530</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>407333</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>456088</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>64,01%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>67,5%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>387562</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>329203</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>416766</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>64,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>459189</t>
+          <t>387090</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>428358</t>
+          <t>365390</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>486251</t>
+          <t>405376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>846751</t>
+          <t>819620</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>786273</t>
+          <t>785890</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>884898</t>
+          <t>853967</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>222418</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>198150</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>248620</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>32,92%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>241015</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>212028</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>300449</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>46,57%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>205893</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>224358</t>
+          <t>186727</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>284780</t>
+          <t>227266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>491353</t>
+          <t>428311</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>449918</t>
+          <t>396636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>554288</t>
+          <t>462690</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>20747</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14134</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>29942</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>10874</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53029</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
